--- a/ARCHIVO_MAESTRO_BIBLIOTECA/04_DATASETS/Coleccion_Fundacional.xlsx
+++ b/ARCHIVO_MAESTRO_BIBLIOTECA/04_DATASETS/Coleccion_Fundacional.xlsx
@@ -11,132 +11,330 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
-  <si>
-    <t>title</t>
-  </si>
-  <si>
-    <t>subtitle</t>
-  </si>
-  <si>
-    <t>author</t>
-  </si>
-  <si>
-    <t>slug</t>
-  </si>
-  <si>
-    <t>genre</t>
-  </si>
-  <si>
-    <t>secondary_genres</t>
-  </si>
-  <si>
-    <t>language</t>
-  </si>
-  <si>
-    <t>country_code</t>
-  </si>
-  <si>
-    <t>year</t>
-  </si>
-  <si>
-    <t>duration_minutes</t>
-  </si>
-  <si>
-    <t>cast_size_min</t>
-  </si>
-  <si>
-    <t>cast_size_max</t>
-  </si>
-  <si>
-    <t>synopsis_short</t>
-  </si>
-  <si>
-    <t>synopsis_full</t>
-  </si>
-  <si>
-    <t>rights_status</t>
-  </si>
-  <si>
-    <t>access_type</t>
-  </si>
-  <si>
-    <t>rights_manager</t>
-  </si>
-  <si>
-    <t>cover_image_url</t>
-  </si>
-  <si>
-    <t>source_name</t>
-  </si>
-  <si>
-    <t>source_url</t>
-  </si>
-  <si>
-    <t>is_library_work</t>
-  </si>
-  <si>
-    <t>notes</t>
-  </si>
-  <si>
-    <t>nombre_completo</t>
-  </si>
-  <si>
-    <t>nombre_canonico</t>
-  </si>
-  <si>
-    <t>nacimiento</t>
-  </si>
-  <si>
-    <t>fallecimiento</t>
-  </si>
-  <si>
-    <t>pais</t>
-  </si>
-  <si>
-    <t>bio_short</t>
-  </si>
-  <si>
-    <t>wikipedia_url</t>
-  </si>
-  <si>
-    <t>notas</t>
-  </si>
-  <si>
-    <t>nombre</t>
-  </si>
-  <si>
-    <t>tipo</t>
-  </si>
-  <si>
-    <t>url</t>
-  </si>
-  <si>
-    <t>licencia</t>
-  </si>
-  <si>
-    <t>descripcion</t>
-  </si>
-  <si>
-    <t>fecha_importacion</t>
-  </si>
-  <si>
-    <t>lote_id</t>
-  </si>
-  <si>
-    <t>obra_titulo</t>
-  </si>
-  <si>
-    <t>obra_slug</t>
-  </si>
-  <si>
-    <t>supabase_id</t>
-  </si>
-  <si>
-    <t>estado</t>
-  </si>
-  <si>
-    <t>validado_por</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="108">
+  <si>
+    <t xml:space="preserve">title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">subtitle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">genre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">secondary_genres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">country_code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">duration_minutes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cast_size_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cast_size_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">synopsis_short</t>
+  </si>
+  <si>
+    <t xml:space="preserve">synopsis_full</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rights_status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">access_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rights_manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cover_image_url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">source_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">source_url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_library_work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La vida es sueño</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedro Calderón de la Barca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">la-vida-es-sueno-calderon-de-la-barca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teatro clásico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drama|Teatro barroco|Teatro del Siglo de Oro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">es</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El príncipe Segismundo descubre que la realidad y los sueños pueden ser indistinguibles, en este drama filosófico del Siglo de Oro español.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drama filosófico en tres jornadas. Segismundo ha sido encerrado desde niño en una torre por su padre, el rey Basilio de Polonia, quien creyó en un horóscopo que auguraba desgracias. Al ser liberado brevemente, sus actos violentos parecen confirmar la profecía. Devuelto a la prisión, le hacen creer que todo fue un sueño. Cuando el pueblo lo libera para combatir a su padre, Segismundo actúa con justicia y clemencia, demostrando que el ser humano puede vencer su destino.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">public_domain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">public_download</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biblioteca Virtual Miguel de Cervantes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cervantesvirtual.com/portales/calderon_de_la_barca/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMPORTADA — piloto P2.2.2B. Supabase ID: 4bfbe073-a590-4974-8dca-95d26187d76a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El alcalde de Zalamea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">el-alcalde-de-zalamea-calderon-de-la-barca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drama de honor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drama|Teatro del Siglo de Oro|Teatro histórico|Comedia de capa y espada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedro Crespo, labrador rico de Zalamea, defiende su honra y la de su hija Isabel frente al abuso de un capitán, en este drama sobre la dignidad y la justicia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En el siglo XVII, el ejército acantona tropas en Zalamea de la Serena. El capitán don Álvaro de Ataide se encapricha de Isabel, hija del rico labrador Pedro Crespo, y la deshonra durante la noche. Nombrado alcalde al día siguiente, Crespo intenta llegar a un acuerdo con el capitán y le ofrece su fortuna entera a cambio del matrimonio. El capitán se niega. Crespo lo apresa, lo juzga y lo condena a garrote, invocando su autoridad jurisdiccional. El rey Felipe II, al llegar, en lugar de castigarlo, lo nombra alcalde perpetuo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PENDIENTE. Fecha provisional: 1636 (composición). Verificar antes de importación definitiva.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El gran teatro del mundo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto sacramental</t>
+  </si>
+  <si>
+    <t xml:space="preserve">el-gran-teatro-del-mundo-calderon-de-la-barca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teatro religioso|Teatro alegórico|Teatro barroco|Teatro del Siglo de Oro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alegoría religiosa en la que Dios encomienda a sus criaturas representar el drama de la vida humana sobre el gran teatro del mundo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto sacramental en una jornada. El Autor (Dios) convoca al Mundo para que disponga un teatro donde sus criaturas representarán la comedia de la vida. A cada personaje alegórico —el Rico, el Rey, la Hermosura, el Labrador, el Pobre, la Discreción— se le asigna un papel sin poder elegirlo. Al final de la representación, cada uno debe rendir cuentas de cómo lo ha desempeñado. La obra concluye con el Sacramento de la Eucaristía como colofón doctrinal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PENDIENTE. Año: 1655 (publicación). Composición debatida: c. 1633-1649. Auto sacramental, duración ~75 min.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La dama duende</t>
+  </si>
+  <si>
+    <t xml:space="preserve">la-dama-duende-calderon-de-la-barca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comedia de enredo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comedia|Teatro barroco|Teatro del Siglo de Oro|Comedia de capa y espada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doña Ángela, viuda encerrada en casa de sus hermanos, se comunica en secreto con el huésped don Manuel a través de una alacena secreta, en esta brillante comedia de enredo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doña Ángela vive encerrada en casa de sus hermanos don Luis y don Juan, que guardan celosamente su viudez. Cuando don Juan trae como huésped al caballero don Manuel, Ángela descubre que entre su aposento y el de su huésped hay una alacena con puerta secreta. A través de ella se introduce en la habitación de don Manuel, le deja cartas y roba objetos sin que él pueda comprender quién es esa misteriosa mujer. La confusión crece con los celos de don Luis y los equívocos de los criados, hasta que el enredo se resuelve y los enamorados pueden unirse.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PENDIENTE.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casa con dos puertas mala es de guardar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">casa-con-dos-puertas-mala-es-de-guardar-calderon-de-la-barca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Félix visita en secreto a su amada Marcela en casa de su amigo Lisardo, sin saber que este corteja a su propia hermana, en esta enredosa comedia de equívocos y puertas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El galán Félix está enamorado de Marcela, que vive junto a su prima Lisarda en una casa con dos puertas. Su amigo Lisardo, que desconoce los amores de Félix con Marcela, también ronda esa casa enamorado de Lisarda. Félix no sabe que Lisardo pretende a su hermana Laura. Las visitas secretas, los malentendidos entre criados, las identidades confundidas y las puertas que permiten entradas incontrolables generan un enredo de creciente comicidad hasta el desenlace donde todos los amores quedan ordenados.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PENDIENTE. Slug largo (59 chars) — verificar comportamiento en frontend.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nombre_completo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nombre_canonico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nacimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fallecimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bio_short</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bio_larga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wikipedia_url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calderón de la Barca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pedro-calderon-de-la-barca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1600-01-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1681-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dramaturgo español del Siglo de Oro. Junto con Lope de Vega, es considerado uno de los grandes maestros del teatro barroco español. Escribió más de cien comedias y ochenta autos sacramentales.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedro Calderón de la Barca nació en Madrid el 17 de enero de 1600 y falleció el 25 de mayo de 1681. Estudió en el Colegio Imperial de los jesuitas de Madrid y en las universidades de Alcalá y Salamanca. Fue soldado antes de dedicarse plenamente al teatro. En 1635 fue nombrado dramaturgo de la corte de Felipe IV. Ordenado sacerdote en 1651, continuó escribiendo autos sacramentales hasta el final de su vida. Es autor de más de cien comedias y ochenta autos sacramentales. Entre sus obras más célebres: La vida es sueño, El alcalde de Zalamea, La dama duende, El gran teatro del mundo y El príncipe constante.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://es.wikipedia.org/wiki/Pedro_Calder%C3%B3n_de_la_Barca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nombre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">licencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">descripcion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">notas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biblioteca digital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cervantesvirtual.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Libre consulta y uso educativo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biblioteca digital española especializada en literatura hispánica. Portal Calderón con ediciones digitales de todas las obras del Lote 001.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuente primaria — Lote 001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biblioteca Digital Hispánica — BNE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://bdh.bne.es</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Libre consulta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biblioteca Digital Hispánica de la Biblioteca Nacional de España. Acceso a fondos digitalizados y manuscritos originales.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuente secundaria — utilizada en piloto P2.2.2B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fecha_importacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lote_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">obra_titulo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">obra_slug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">supabase_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">validado_por</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lote_001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La vida es sueno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4bfbe073-a590-4974-8dca-95d26187d76a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMPORTADA_PILOTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sistema</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piloto P2.2.2B - importacion manual via Supabase MCP</t>
   </si>
 </sst>
 </file>
@@ -246,6 +444,304 @@
         <v>21</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2">
+        <v>1635</v>
+      </c>
+      <c r="J2">
+        <v>120</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>8</v>
+      </c>
+      <c r="M2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" t="s">
+        <v>32</v>
+      </c>
+      <c r="S2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T2" t="s">
+        <v>34</v>
+      </c>
+      <c r="U2" t="s">
+        <v>35</v>
+      </c>
+      <c r="V2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3">
+        <v>1636</v>
+      </c>
+      <c r="J3">
+        <v>110</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
+      <c r="L3">
+        <v>12</v>
+      </c>
+      <c r="M3" t="s">
+        <v>41</v>
+      </c>
+      <c r="N3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" t="s">
+        <v>32</v>
+      </c>
+      <c r="S3" t="s">
+        <v>33</v>
+      </c>
+      <c r="T3" t="s">
+        <v>34</v>
+      </c>
+      <c r="U3" t="s">
+        <v>35</v>
+      </c>
+      <c r="V3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4">
+        <v>1655</v>
+      </c>
+      <c r="J4">
+        <v>75</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="L4">
+        <v>10</v>
+      </c>
+      <c r="M4" t="s">
+        <v>48</v>
+      </c>
+      <c r="N4" t="s">
+        <v>49</v>
+      </c>
+      <c r="O4" t="s">
+        <v>31</v>
+      </c>
+      <c r="P4" t="s">
+        <v>32</v>
+      </c>
+      <c r="S4" t="s">
+        <v>33</v>
+      </c>
+      <c r="T4" t="s">
+        <v>34</v>
+      </c>
+      <c r="U4" t="s">
+        <v>35</v>
+      </c>
+      <c r="V4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5">
+        <v>1629</v>
+      </c>
+      <c r="J5">
+        <v>100</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>9</v>
+      </c>
+      <c r="M5" t="s">
+        <v>55</v>
+      </c>
+      <c r="N5" t="s">
+        <v>56</v>
+      </c>
+      <c r="O5" t="s">
+        <v>31</v>
+      </c>
+      <c r="P5" t="s">
+        <v>32</v>
+      </c>
+      <c r="S5" t="s">
+        <v>33</v>
+      </c>
+      <c r="T5" t="s">
+        <v>34</v>
+      </c>
+      <c r="U5" t="s">
+        <v>35</v>
+      </c>
+      <c r="V5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6">
+        <v>1629</v>
+      </c>
+      <c r="J6">
+        <v>100</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>9</v>
+      </c>
+      <c r="M6" t="s">
+        <v>60</v>
+      </c>
+      <c r="N6" t="s">
+        <v>61</v>
+      </c>
+      <c r="O6" t="s">
+        <v>31</v>
+      </c>
+      <c r="P6" t="s">
+        <v>32</v>
+      </c>
+      <c r="S6" t="s">
+        <v>33</v>
+      </c>
+      <c r="T6" t="s">
+        <v>34</v>
+      </c>
+      <c r="U6" t="s">
+        <v>35</v>
+      </c>
+      <c r="V6" t="s">
+        <v>62</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -255,31 +751,60 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="B1" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="C1" t="s">
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="E1" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="F1" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="G1" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="H1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F2" t="s">
         <v>28</v>
       </c>
-      <c r="I1" t="s">
-        <v>29</v>
+      <c r="G2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I2" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -291,22 +816,62 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="B1" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="C1" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="D1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
         <v>33</v>
       </c>
-      <c r="E1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" t="s">
-        <v>29</v>
+      <c r="B2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F3" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -318,28 +883,54 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="C1" t="s">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="D1" t="s">
-        <v>38</v>
+        <v>97</v>
       </c>
       <c r="E1" t="s">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="F1" t="s">
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="G1" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="H1" t="s">
-        <v>29</v>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H2" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
